--- a/survey_templates/042_diy_beauty_practice_survey--survey_templates.xlsx
+++ b/survey_templates/042_diy_beauty_practice_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C65"/>
+  <dimension ref="A1:C64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1262,17 +1262,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>products_used_choices</t>
+          <t>practice_motivations_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>haircare</t>
+          <t>to_feel_more_confident</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Haircare</t>
+          <t>To feel more confident</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>to_feel_more_confident</t>
+          <t>to_feel_more_attractive</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>To feel more confident</t>
+          <t>To feel more attractive</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>to_feel_more_attractive</t>
+          <t>to_improve_skin_health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>To feel more attractive</t>
+          <t>To improve skin health</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>to_improve_skin_health</t>
+          <t>to_improve_hair_health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>To improve skin health</t>
+          <t>To improve hair health</t>
         </is>
       </c>
     </row>
@@ -1335,29 +1335,29 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>to_improve_hair_health</t>
+          <t>to_feel_more_beautiful</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>To improve hair health</t>
+          <t>To feel more beautiful</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>practice_motivations_choices</t>
+          <t>challenges_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>to_feel_more_beautiful</t>
+          <t>not_enough_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>To feel more beautiful</t>
+          <t>Not enough time</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_enough_time</t>
+          <t>not_enough_money</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Not enough time</t>
+          <t>Not enough money</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_enough_money</t>
+          <t>not_enough_knowledge</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Not enough money</t>
+          <t>Not enough knowledge</t>
         </is>
       </c>
     </row>
@@ -1403,29 +1403,29 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_enough_knowledge</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Not enough knowledge</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>challenges_choices</t>
+          <t>favorite_beauty_product_type_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>skincare</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Skincare</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>skincare</t>
+          <t>haircare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>Haircare</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>haircare</t>
+          <t>fragrance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Haircare</t>
+          <t>Fragrance</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>fragrance</t>
+          <t>makeup</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Fragrance</t>
+          <t>Makeup</t>
         </is>
       </c>
     </row>
@@ -1488,29 +1488,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>makeup</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Makeup</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>favorite_beauty_product_type_choices</t>
+          <t>beauty_interests_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>skincare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Skincare</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>skincare</t>
+          <t>haircare</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>Haircare</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>haircare</t>
+          <t>fragrance</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Haircare</t>
+          <t>Fragrance</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>fragrance</t>
+          <t>makeup</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fragrance</t>
+          <t>Makeup</t>
         </is>
       </c>
     </row>
@@ -1573,29 +1573,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>makeup</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Makeup</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>beauty_interests_choices</t>
+          <t>practice_frequency_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>several_times_a_week</t>
+          <t>several_times_a_month</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Several times a week</t>
+          <t>Several times a month</t>
         </is>
       </c>
     </row>
@@ -1641,29 +1641,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>several_times_a_month</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Several times a month</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>practice_frequency_choices</t>
+          <t>practice_mission_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>to_feel_more_confident</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>To feel more confident</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>to_feel_more_confident</t>
+          <t>to_feel_more_beautiful</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>To feel more confident</t>
+          <t>To feel more beautiful</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>to_feel_more_beautiful</t>
+          <t>to_improve_skin_health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>To feel more beautiful</t>
+          <t>To improve skin health</t>
         </is>
       </c>
     </row>
@@ -1709,29 +1709,29 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>to_improve_skin_health</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>To improve skin health</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>practice_mission_choices</t>
+          <t>practice_influence_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>often</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Often</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1777,29 +1777,29 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>practice_influence_choices</t>
+          <t>practice_influencer_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>influencer</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Influencer</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>influencer</t>
+          <t>celebrity</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Influencer</t>
+          <t>Celebrity</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>celebrity</t>
+          <t>family/friends</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Celebrity</t>
+          <t>Family/friends</t>
         </is>
       </c>
     </row>
@@ -1845,29 +1845,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>family/friends</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Family/friends</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>practice_influencer_choices</t>
+          <t>practice_motivation_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>to_feel_more_beautiful</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>To feel more beautiful</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>to_feel_more_beautiful</t>
+          <t>to_feel_more_confident</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>To feel more beautiful</t>
+          <t>To feel more confident</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>to_feel_more_confident</t>
+          <t>to_improve_skin_health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>To feel more confident</t>
+          <t>To improve skin health</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>to_improve_skin_health</t>
+          <t>to_improve_hair_health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>To improve skin health</t>
+          <t>To improve hair health</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>to_improve_hair_health</t>
+          <t>to_feel_more_connected</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>To improve hair health</t>
+          <t>To feel more connected</t>
         </is>
       </c>
     </row>
@@ -1947,29 +1947,29 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>to_feel_more_connected</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>To feel more connected</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>practice_motivation_choices</t>
+          <t>practice_frequency_change_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>several_times_a_week</t>
+          <t>several_times_a_month</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Several times a week</t>
+          <t>Several times a month</t>
         </is>
       </c>
     </row>
@@ -2015,29 +2015,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>several_times_a_month</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Several times a month</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>practice_frequency_change_choices</t>
+          <t>favorite_beauty_product_category_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>skincare</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Skincare</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>skincare</t>
+          <t>haircare</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Skincare</t>
+          <t>Haircare</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>haircare</t>
+          <t>fragrance</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Haircare</t>
+          <t>Fragrance</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>fragrance</t>
+          <t>makeup</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Fragrance</t>
+          <t>Makeup</t>
         </is>
       </c>
     </row>
@@ -2100,29 +2100,29 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>makeup</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Makeup</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>favorite_beauty_product_category_choices</t>
+          <t>practice_frequency_mood_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>when_i'm_feeling_anxious</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>When I'm feeling anxious</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>when_i'm_feeling_anxious</t>
+          <t>when_i'm_feeling_stressed</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>When I'm feeling anxious</t>
+          <t>When I'm feeling stressed</t>
         </is>
       </c>
     </row>
@@ -2151,12 +2151,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>when_i'm_feeling_stressed</t>
+          <t>when_i'm_feeling_happy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>When I'm feeling stressed</t>
+          <t>When I'm feeling happy</t>
         </is>
       </c>
     </row>
@@ -2168,12 +2168,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>when_i'm_feeling_happy</t>
+          <t>when_i'm_feeling_sad</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>When I'm feeling happy</t>
+          <t>When I'm feeling sad</t>
         </is>
       </c>
     </row>
@@ -2185,27 +2185,10 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>when_i'm_feeling_sad</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
-        <is>
-          <t>When I'm feeling sad</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>practice_frequency_mood_choices</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
